--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G72"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -1995,9 +1995,78 @@
         <v>24/08/2026, 20:03:34</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B70" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>10</v>
+      </c>
+      <c r="E70" t="str">
+        <v>400</v>
+      </c>
+      <c r="F70" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G70" t="str">
+        <v>18/09/2026, 00:54:53</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B71" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>10</v>
+      </c>
+      <c r="E71" t="str">
+        <v>390</v>
+      </c>
+      <c r="F71" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G71" t="str">
+        <v>18/09/2026, 00:55:57</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B72" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>10</v>
+      </c>
+      <c r="E72" t="str">
+        <v>380</v>
+      </c>
+      <c r="F72" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G72" t="str">
+        <v>18/09/2026, 00:57:42</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G72"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G87"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -2064,9 +2064,354 @@
         <v>18/09/2026, 00:57:42</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B73" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>10</v>
+      </c>
+      <c r="E73" t="str">
+        <v>370</v>
+      </c>
+      <c r="F73" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G73" t="str">
+        <v>18/09/2026, 11:22:33</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B74" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>10</v>
+      </c>
+      <c r="E74" t="str">
+        <v>360</v>
+      </c>
+      <c r="F74" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G74" t="str">
+        <v>18/09/2026, 11:31:14</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B75" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>10</v>
+      </c>
+      <c r="E75" t="str">
+        <v>350</v>
+      </c>
+      <c r="F75" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G75" t="str">
+        <v>18/09/2026, 11:32:34</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B76" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <v>10</v>
+      </c>
+      <c r="E76" t="str">
+        <v>340</v>
+      </c>
+      <c r="F76" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G76" t="str">
+        <v>18/09/2026, 11:34:20</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B77" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <v>10</v>
+      </c>
+      <c r="E77" t="str">
+        <v>330</v>
+      </c>
+      <c r="F77" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G77" t="str">
+        <v>18/09/2026, 11:35:48</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B78" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <v>10</v>
+      </c>
+      <c r="E78" t="str">
+        <v>320</v>
+      </c>
+      <c r="F78" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G78" t="str">
+        <v>18/09/2026, 11:36:24</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B79" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>10</v>
+      </c>
+      <c r="E79" t="str">
+        <v>310</v>
+      </c>
+      <c r="F79" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G79" t="str">
+        <v>18/09/2026, 11:37:48</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B80" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80">
+        <v>10</v>
+      </c>
+      <c r="E80" t="str">
+        <v>300</v>
+      </c>
+      <c r="F80" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G80" t="str">
+        <v>18/09/2026, 14:37:00</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B81" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81">
+        <v>10</v>
+      </c>
+      <c r="E81" t="str">
+        <v>290</v>
+      </c>
+      <c r="F81" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G81" t="str">
+        <v>18/09/2026, 14:39:09</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B82" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82">
+        <v>10</v>
+      </c>
+      <c r="E82" t="str">
+        <v>280</v>
+      </c>
+      <c r="F82" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G82" t="str">
+        <v>18/09/2026, 14:40:04</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B83" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+      <c r="D83">
+        <v>10</v>
+      </c>
+      <c r="E83" t="str">
+        <v>270</v>
+      </c>
+      <c r="F83" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G83" t="str">
+        <v>18/09/2026, 14:54:02</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B84" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <v>10</v>
+      </c>
+      <c r="E84" t="str">
+        <v>260</v>
+      </c>
+      <c r="F84" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G84" t="str">
+        <v>18/09/2026, 14:55:33</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B85" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85">
+        <v>10</v>
+      </c>
+      <c r="E85" t="str">
+        <v>250</v>
+      </c>
+      <c r="F85" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G85" t="str">
+        <v>18/09/2026, 14:59:05</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B86" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <v>10</v>
+      </c>
+      <c r="E86" t="str">
+        <v>240</v>
+      </c>
+      <c r="F86" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G86" t="str">
+        <v>18/09/2026, 15:15:36</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B87" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>10</v>
+      </c>
+      <c r="E87" t="str">
+        <v>230</v>
+      </c>
+      <c r="F87" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G87" t="str">
+        <v>18/09/2026, 15:18:18</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G72"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G87"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G90"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -2409,9 +2409,78 @@
         <v>18/09/2026, 15:18:18</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B88" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <v>10</v>
+      </c>
+      <c r="E88" t="str">
+        <v>220</v>
+      </c>
+      <c r="F88" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G88" t="str">
+        <v>19/09/2026, 14:59:25</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B89" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <v>10</v>
+      </c>
+      <c r="E89" t="str">
+        <v>210</v>
+      </c>
+      <c r="F89" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G89" t="str">
+        <v>19/09/2026, 15:01:14</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B90" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <v>10</v>
+      </c>
+      <c r="E90" t="str">
+        <v>200</v>
+      </c>
+      <c r="F90" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G90" t="str">
+        <v>19/09/2026, 15:04:24</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G90"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G92"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -2478,9 +2478,55 @@
         <v>19/09/2026, 15:04:24</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B91" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+      <c r="D91">
+        <v>10</v>
+      </c>
+      <c r="E91" t="str">
+        <v>190</v>
+      </c>
+      <c r="F91" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G91" t="str">
+        <v>19/09/2026, 20:40:52</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B92" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
+      <c r="D92">
+        <v>10</v>
+      </c>
+      <c r="E92" t="str">
+        <v>180</v>
+      </c>
+      <c r="F92" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G92" t="str">
+        <v>19/09/2026, 21:49:25</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G90"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G92"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G101"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -2524,9 +2524,216 @@
         <v>19/09/2026, 21:49:25</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B93" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
+      <c r="D93">
+        <v>10</v>
+      </c>
+      <c r="E93" t="str">
+        <v>170</v>
+      </c>
+      <c r="F93" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G93" t="str">
+        <v>20/09/2026, 10:42:52</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B94" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
+      <c r="D94">
+        <v>10</v>
+      </c>
+      <c r="E94" t="str">
+        <v>160</v>
+      </c>
+      <c r="F94" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G94" t="str">
+        <v>20/09/2026, 13:34:03</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B95" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
+      <c r="D95">
+        <v>10</v>
+      </c>
+      <c r="E95" t="str">
+        <v>150</v>
+      </c>
+      <c r="F95" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G95" t="str">
+        <v>20/09/2026, 14:53:15</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B96" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
+      <c r="D96">
+        <v>10</v>
+      </c>
+      <c r="E96" t="str">
+        <v>140</v>
+      </c>
+      <c r="F96" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G96" t="str">
+        <v>20/09/2026, 18:55:22</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B97" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+      <c r="D97">
+        <v>10</v>
+      </c>
+      <c r="E97" t="str">
+        <v>130</v>
+      </c>
+      <c r="F97" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G97" t="str">
+        <v>20/09/2026, 18:56:10</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B98" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+      <c r="D98">
+        <v>10</v>
+      </c>
+      <c r="E98" t="str">
+        <v>120</v>
+      </c>
+      <c r="F98" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G98" t="str">
+        <v>20/09/2026, 19:00:24</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B99" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+      <c r="D99">
+        <v>10</v>
+      </c>
+      <c r="E99" t="str">
+        <v>110</v>
+      </c>
+      <c r="F99" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G99" t="str">
+        <v>20/09/2026, 19:05:33</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B100" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="D100">
+        <v>10</v>
+      </c>
+      <c r="E100" t="str">
+        <v>100</v>
+      </c>
+      <c r="F100" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G100" t="str">
+        <v>20/09/2026, 19:06:35</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B101" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101">
+        <v>10</v>
+      </c>
+      <c r="E101" t="str">
+        <v>90</v>
+      </c>
+      <c r="F101" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G101" t="str">
+        <v>20/09/2026, 19:08:49</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G92"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G101"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G111"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -2731,9 +2731,239 @@
         <v>20/09/2026, 19:08:49</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B102" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+      <c r="D102">
+        <v>10</v>
+      </c>
+      <c r="E102" t="str">
+        <v>80</v>
+      </c>
+      <c r="F102" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G102" t="str">
+        <v>20/09/2026, 20:29:42</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B103" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+      <c r="D103">
+        <v>10</v>
+      </c>
+      <c r="E103" t="str">
+        <v>70</v>
+      </c>
+      <c r="F103" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G103" t="str">
+        <v>20/09/2026, 20:32:00</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B104" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+      <c r="D104">
+        <v>10</v>
+      </c>
+      <c r="E104" t="str">
+        <v>60</v>
+      </c>
+      <c r="F104" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G104" t="str">
+        <v>20/09/2026, 20:32:36</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B105" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
+      <c r="D105">
+        <v>10</v>
+      </c>
+      <c r="E105" t="str">
+        <v>50</v>
+      </c>
+      <c r="F105" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G105" t="str">
+        <v>20/09/2026, 20:34:02</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B106" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+      <c r="D106">
+        <v>10</v>
+      </c>
+      <c r="E106" t="str">
+        <v>40</v>
+      </c>
+      <c r="F106" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G106" t="str">
+        <v>20/09/2026, 20:35:15</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B107" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
+      </c>
+      <c r="D107">
+        <v>10</v>
+      </c>
+      <c r="E107" t="str">
+        <v>30</v>
+      </c>
+      <c r="F107" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G107" t="str">
+        <v>20/09/2026, 20:36:56</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B108" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C108">
+        <v>0</v>
+      </c>
+      <c r="D108">
+        <v>10</v>
+      </c>
+      <c r="E108" t="str">
+        <v>20</v>
+      </c>
+      <c r="F108" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G108" t="str">
+        <v>20/09/2026, 20:48:52</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B109" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C109">
+        <v>0</v>
+      </c>
+      <c r="D109">
+        <v>10</v>
+      </c>
+      <c r="E109" t="str">
+        <v>10</v>
+      </c>
+      <c r="F109" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G109" t="str">
+        <v>20/09/2026, 21:14:06</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B110" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+      <c r="D110">
+        <v>10</v>
+      </c>
+      <c r="E110" t="str">
+        <v>0</v>
+      </c>
+      <c r="F110" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G110" t="str">
+        <v>21/09/2026, 06:54:19</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B111" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C111">
+        <v>0</v>
+      </c>
+      <c r="D111">
+        <v>10</v>
+      </c>
+      <c r="E111" t="str">
+        <v>990</v>
+      </c>
+      <c r="F111" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G111" t="str">
+        <v>21/09/2026, 07:25:13</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G111"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G114"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -2961,9 +2961,78 @@
         <v>21/09/2026, 07:25:13</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B112" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+      <c r="D112">
+        <v>10</v>
+      </c>
+      <c r="E112" t="str">
+        <v>980</v>
+      </c>
+      <c r="F112" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G112" t="str">
+        <v>21/09/2026, 16:23:53</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B113" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+      <c r="D113">
+        <v>10</v>
+      </c>
+      <c r="E113" t="str">
+        <v>970</v>
+      </c>
+      <c r="F113" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G113" t="str">
+        <v>21/09/2026, 16:24:21</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B114" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="D114">
+        <v>10</v>
+      </c>
+      <c r="E114" t="str">
+        <v>960</v>
+      </c>
+      <c r="F114" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G114" t="str">
+        <v>21/09/2026, 16:56:16</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G111"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G114"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G119"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -3030,9 +3030,124 @@
         <v>21/09/2026, 16:56:16</v>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B115" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="D115">
+        <v>10</v>
+      </c>
+      <c r="E115" t="str">
+        <v>950</v>
+      </c>
+      <c r="F115" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G115" t="str">
+        <v>21/09/2026, 21:11:47</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B116" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+      <c r="D116">
+        <v>10</v>
+      </c>
+      <c r="E116" t="str">
+        <v>940</v>
+      </c>
+      <c r="F116" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G116" t="str">
+        <v>21/09/2026, 21:12:49</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B117" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="D117">
+        <v>10</v>
+      </c>
+      <c r="E117" t="str">
+        <v>930</v>
+      </c>
+      <c r="F117" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G117" t="str">
+        <v>22/09/2026, 09:11:35</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B118" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+      <c r="D118">
+        <v>10</v>
+      </c>
+      <c r="E118" t="str">
+        <v>920</v>
+      </c>
+      <c r="F118" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G118" t="str">
+        <v>22/09/2026, 12:07:38</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B119" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C119">
+        <v>0</v>
+      </c>
+      <c r="D119">
+        <v>10</v>
+      </c>
+      <c r="E119" t="str">
+        <v>910</v>
+      </c>
+      <c r="F119" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G119" t="str">
+        <v>22/09/2026, 12:12:13</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G114"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G119"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G122"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -3145,9 +3145,78 @@
         <v>22/09/2026, 12:12:13</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B120" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
+      <c r="D120">
+        <v>10</v>
+      </c>
+      <c r="E120" t="str">
+        <v>900</v>
+      </c>
+      <c r="F120" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G120" t="str">
+        <v>22/09/2026, 17:49:36</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B121" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+      <c r="D121">
+        <v>10</v>
+      </c>
+      <c r="E121" t="str">
+        <v>890</v>
+      </c>
+      <c r="F121" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G121" t="str">
+        <v>22/09/2026, 18:17:41</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B122" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C122">
+        <v>0</v>
+      </c>
+      <c r="D122">
+        <v>10</v>
+      </c>
+      <c r="E122" t="str">
+        <v>880</v>
+      </c>
+      <c r="F122" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G122" t="str">
+        <v>22/09/2026, 18:20:02</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G119"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G122"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G124"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -3214,9 +3214,55 @@
         <v>22/09/2026, 18:20:02</v>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B123" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C123">
+        <v>0</v>
+      </c>
+      <c r="D123">
+        <v>10</v>
+      </c>
+      <c r="E123" t="str">
+        <v>870</v>
+      </c>
+      <c r="F123" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G123" t="str">
+        <v>22/09/2026, 22:20:02</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B124" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C124">
+        <v>0</v>
+      </c>
+      <c r="D124">
+        <v>10</v>
+      </c>
+      <c r="E124" t="str">
+        <v>860</v>
+      </c>
+      <c r="F124" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G124" t="str">
+        <v>22/09/2026, 22:47:20</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G122"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G124"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G129"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -3260,9 +3260,124 @@
         <v>22/09/2026, 22:47:20</v>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B125" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C125">
+        <v>0</v>
+      </c>
+      <c r="D125">
+        <v>10</v>
+      </c>
+      <c r="E125" t="str">
+        <v>850</v>
+      </c>
+      <c r="F125" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G125" t="str">
+        <v>23/09/2026, 06:52:19</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B126" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126">
+        <v>10</v>
+      </c>
+      <c r="E126" t="str">
+        <v>840</v>
+      </c>
+      <c r="F126" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G126" t="str">
+        <v>23/09/2026, 07:00:38</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B127" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
+      </c>
+      <c r="D127">
+        <v>10</v>
+      </c>
+      <c r="E127" t="str">
+        <v>830</v>
+      </c>
+      <c r="F127" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G127" t="str">
+        <v>23/09/2026, 07:01:20</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B128" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
+      <c r="D128">
+        <v>10</v>
+      </c>
+      <c r="E128" t="str">
+        <v>820</v>
+      </c>
+      <c r="F128" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G128" t="str">
+        <v>23/09/2026, 07:37:55</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B129" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
+      <c r="D129">
+        <v>10</v>
+      </c>
+      <c r="E129" t="str">
+        <v>810</v>
+      </c>
+      <c r="F129" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G129" t="str">
+        <v>23/09/2026, 07:38:40</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G124"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G129"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G130"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -3375,9 +3375,32 @@
         <v>23/09/2026, 07:38:40</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B130" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+      <c r="D130">
+        <v>10</v>
+      </c>
+      <c r="E130" t="str">
+        <v>800</v>
+      </c>
+      <c r="F130" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G130" t="str">
+        <v>23/09/2026, 09:02:58</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G130"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G131"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -3398,9 +3398,32 @@
         <v>23/09/2026, 09:02:58</v>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B131" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+      <c r="D131">
+        <v>10</v>
+      </c>
+      <c r="E131" t="str">
+        <v>790</v>
+      </c>
+      <c r="F131" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G131" t="str">
+        <v>23/09/2026, 21:04:50</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G131"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G137"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -3421,9 +3421,147 @@
         <v>23/09/2026, 21:04:50</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B132" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C132">
+        <v>0</v>
+      </c>
+      <c r="D132">
+        <v>10</v>
+      </c>
+      <c r="E132" t="str">
+        <v>780</v>
+      </c>
+      <c r="F132" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G132" t="str">
+        <v>24/09/2026, 17:12:23</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B133" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+      <c r="D133">
+        <v>10</v>
+      </c>
+      <c r="E133" t="str">
+        <v>770</v>
+      </c>
+      <c r="F133" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G133" t="str">
+        <v>24/09/2026, 17:15:15</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B134" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C134">
+        <v>0</v>
+      </c>
+      <c r="D134">
+        <v>10</v>
+      </c>
+      <c r="E134" t="str">
+        <v>760</v>
+      </c>
+      <c r="F134" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G134" t="str">
+        <v>24/09/2026, 17:15:50</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B135" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C135">
+        <v>0</v>
+      </c>
+      <c r="D135">
+        <v>10</v>
+      </c>
+      <c r="E135" t="str">
+        <v>750</v>
+      </c>
+      <c r="F135" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G135" t="str">
+        <v>24/09/2026, 17:16:51</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B136" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C136">
+        <v>0</v>
+      </c>
+      <c r="D136">
+        <v>10</v>
+      </c>
+      <c r="E136" t="str">
+        <v>740</v>
+      </c>
+      <c r="F136" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G136" t="str">
+        <v>24/09/2026, 17:22:52</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B137" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C137">
+        <v>0</v>
+      </c>
+      <c r="D137">
+        <v>10</v>
+      </c>
+      <c r="E137" t="str">
+        <v>730</v>
+      </c>
+      <c r="F137" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G137" t="str">
+        <v>24/09/2026, 17:29:36</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G131"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G137"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G137"/>
+  <dimension ref="A1:G138"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -3559,9 +3559,32 @@
         <v>24/09/2026, 17:29:36</v>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B138" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C138">
+        <v>0</v>
+      </c>
+      <c r="D138">
+        <v>10</v>
+      </c>
+      <c r="E138" t="str">
+        <v>720</v>
+      </c>
+      <c r="F138" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G138" t="str">
+        <v>26/09/2026, 09:14:59</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G137"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G138"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G143"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -3582,9 +3582,124 @@
         <v>26/09/2026, 09:14:59</v>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B139" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C139">
+        <v>0</v>
+      </c>
+      <c r="D139">
+        <v>10</v>
+      </c>
+      <c r="E139" t="str">
+        <v>710</v>
+      </c>
+      <c r="F139" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G139" t="str">
+        <v>27/09/2026, 11:32:46</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B140" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C140">
+        <v>0</v>
+      </c>
+      <c r="D140">
+        <v>10</v>
+      </c>
+      <c r="E140" t="str">
+        <v>700</v>
+      </c>
+      <c r="F140" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G140" t="str">
+        <v>27/09/2026, 11:35:33</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B141" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C141">
+        <v>0</v>
+      </c>
+      <c r="D141">
+        <v>10</v>
+      </c>
+      <c r="E141" t="str">
+        <v>690</v>
+      </c>
+      <c r="F141" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G141" t="str">
+        <v>27/09/2026, 11:41:32</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B142" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C142">
+        <v>0</v>
+      </c>
+      <c r="D142">
+        <v>10</v>
+      </c>
+      <c r="E142" t="str">
+        <v>680</v>
+      </c>
+      <c r="F142" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G142" t="str">
+        <v>27/09/2026, 11:51:11</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B143" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C143">
+        <v>0</v>
+      </c>
+      <c r="D143">
+        <v>10</v>
+      </c>
+      <c r="E143" t="str">
+        <v>670</v>
+      </c>
+      <c r="F143" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G143" t="str">
+        <v>27/09/2026, 12:03:06</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G138"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G143"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G144"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -3697,9 +3697,32 @@
         <v>27/09/2026, 12:03:06</v>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B144" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+      <c r="D144">
+        <v>10</v>
+      </c>
+      <c r="E144" t="str">
+        <v>660</v>
+      </c>
+      <c r="F144" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G144" t="str">
+        <v>29/09/2026, 11:46:18</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G143"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G144"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G150"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -3720,9 +3720,147 @@
         <v>29/09/2026, 11:46:18</v>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B145" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C145">
+        <v>0</v>
+      </c>
+      <c r="D145">
+        <v>10</v>
+      </c>
+      <c r="E145" t="str">
+        <v>650</v>
+      </c>
+      <c r="F145" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G145" t="str">
+        <v>30/09/2026, 22:03:27</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B146" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+      <c r="D146">
+        <v>10</v>
+      </c>
+      <c r="E146" t="str">
+        <v>640</v>
+      </c>
+      <c r="F146" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G146" t="str">
+        <v>30/09/2026, 22:05:14</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B147" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
+      <c r="D147">
+        <v>10</v>
+      </c>
+      <c r="E147" t="str">
+        <v>630</v>
+      </c>
+      <c r="F147" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G147" t="str">
+        <v>30/09/2026, 22:05:49</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B148" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C148">
+        <v>0</v>
+      </c>
+      <c r="D148">
+        <v>10</v>
+      </c>
+      <c r="E148" t="str">
+        <v>620</v>
+      </c>
+      <c r="F148" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G148" t="str">
+        <v>30/09/2026, 22:07:32</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B149" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C149">
+        <v>0</v>
+      </c>
+      <c r="D149">
+        <v>10</v>
+      </c>
+      <c r="E149" t="str">
+        <v>610</v>
+      </c>
+      <c r="F149" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G149" t="str">
+        <v>30/09/2026, 22:19:18</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B150" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C150">
+        <v>0</v>
+      </c>
+      <c r="D150">
+        <v>10</v>
+      </c>
+      <c r="E150" t="str">
+        <v>600</v>
+      </c>
+      <c r="F150" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G150" t="str">
+        <v>30/09/2026, 22:21:42</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G144"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G150"/>
   </ignoredErrors>
 </worksheet>
 </file>